--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.02036687902783</v>
+        <v>5.040809617842022</v>
       </c>
       <c r="D2" t="n">
-        <v>31.49093765010834</v>
+        <v>5.117277368142605</v>
       </c>
       <c r="E2" t="n">
-        <v>14.91086609009336</v>
+        <v>2.423015739640171</v>
       </c>
       <c r="F2" t="n">
-        <v>8.624703688404681</v>
+        <v>1.401514349365761</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.92133669927351</v>
+        <v>3.399717213631946</v>
       </c>
       <c r="D3" t="n">
-        <v>21.38474914861949</v>
+        <v>3.475021736650667</v>
       </c>
       <c r="E3" t="n">
-        <v>14.91086609009336</v>
+        <v>2.423015739640171</v>
       </c>
       <c r="F3" t="n">
-        <v>8.624703688404681</v>
+        <v>1.401514349365761</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.37173398780006</v>
+        <v>1.847906773017509</v>
       </c>
       <c r="D4" t="n">
-        <v>10.90584888959437</v>
+        <v>1.772200444559085</v>
       </c>
       <c r="E4" t="n">
-        <v>14.91086609009336</v>
+        <v>2.423015739640171</v>
       </c>
       <c r="F4" t="n">
-        <v>8.624703688404681</v>
+        <v>1.401514349365761</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.68152940032794</v>
+        <v>4.98574852755329</v>
       </c>
       <c r="D5" t="n">
-        <v>32.90453539944445</v>
+        <v>5.346987002409723</v>
       </c>
       <c r="E5" t="n">
-        <v>14.91086609009336</v>
+        <v>2.423015739640171</v>
       </c>
       <c r="F5" t="n">
-        <v>8.624703688404681</v>
+        <v>1.401514349365761</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>56.19732827470911</v>
+        <v>9.132065844640232</v>
       </c>
       <c r="D6" t="n">
-        <v>25.75630032068928</v>
+        <v>4.185398802112009</v>
       </c>
       <c r="E6" t="n">
-        <v>14.91086609009336</v>
+        <v>2.423015739640171</v>
       </c>
       <c r="F6" t="n">
-        <v>8.624703688404681</v>
+        <v>1.401514349365761</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>46.16685261703741</v>
+        <v>7.50211355026858</v>
       </c>
       <c r="D7" t="n">
-        <v>37.0130245348883</v>
+        <v>6.014616486919349</v>
       </c>
       <c r="E7" t="n">
-        <v>14.91086609009336</v>
+        <v>2.423015739640171</v>
       </c>
       <c r="F7" t="n">
-        <v>8.624703688404681</v>
+        <v>1.401514349365761</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
